--- a/digital-products/wedding-angbao-planner/singapore-wedding-cashflow-angbao-planner-2026.xlsx
+++ b/digital-products/wedding-angbao-planner/singapore-wedding-cashflow-angbao-planner-2026.xlsx
@@ -35,8 +35,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="60" formatCode="&quot;S$&quot;#,##0"/>
+    <numFmt numFmtId="61" formatCode="0.0%"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -67,8 +69,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="60" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="61" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -558,7 +562,7 @@
       <c r="B8" t="str">
         <v>Package price per table (S$) — Market estimate</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="1">
         <v>1288</v>
       </c>
       <c r="D8" t="str">
@@ -569,7 +573,7 @@
       <c r="B9" t="str">
         <v>Service charge</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="2">
         <v>0.1</v>
       </c>
       <c r="D9" t="str">
@@ -580,7 +584,7 @@
       <c r="B10" t="str">
         <v>GST</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="2">
         <v>0.09</v>
       </c>
       <c r="D10" t="str">
@@ -596,7 +600,7 @@
       <c r="B13" t="str">
         <v>Bridal package (gown, suit, makeup, hair)</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="1">
         <v>4000</v>
       </c>
     </row>
@@ -604,7 +608,7 @@
       <c r="B14" t="str">
         <v>Photography</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="1">
         <v>3500</v>
       </c>
     </row>
@@ -612,7 +616,7 @@
       <c r="B15" t="str">
         <v>Videography</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="1">
         <v>2500</v>
       </c>
     </row>
@@ -620,7 +624,7 @@
       <c r="B16" t="str">
         <v>Décor (beyond venue-provided)</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="1">
         <v>1500</v>
       </c>
     </row>
@@ -628,7 +632,7 @@
       <c r="B17" t="str">
         <v>Rings</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="1">
         <v>3000</v>
       </c>
     </row>
@@ -636,7 +640,7 @@
       <c r="B18" t="str">
         <v>Attire / extra outfits</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="1">
         <v>1200</v>
       </c>
     </row>
@@ -644,7 +648,7 @@
       <c r="B19" t="str">
         <v>Invitations &amp; stationery</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="1">
         <v>500</v>
       </c>
     </row>
@@ -652,7 +656,7 @@
       <c r="B20" t="str">
         <v>Solemnisation / ROM</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="1">
         <v>100</v>
       </c>
     </row>
@@ -660,7 +664,7 @@
       <c r="B21" t="str">
         <v>Transport</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="1">
         <v>800</v>
       </c>
     </row>
@@ -668,7 +672,7 @@
       <c r="B22" t="str">
         <v>Cultural items / customs</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="1">
         <v>1500</v>
       </c>
     </row>
@@ -676,7 +680,7 @@
       <c r="B23" t="str">
         <v>Miscellaneous</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="1">
         <v>800</v>
       </c>
     </row>
@@ -684,7 +688,7 @@
       <c r="B24" t="str">
         <v>User-defined expenses</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="1">
         <v>0</v>
       </c>
     </row>
@@ -692,7 +696,7 @@
       <c r="B25" t="str">
         <v>TOTAL NON-BANQUET COST</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="1">
         <f>SUM(C13:C24)</f>
         <v>0</v>
       </c>
@@ -711,7 +715,7 @@
       <c r="B29" t="str">
         <v>Conservative (per guest)</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="1">
         <v>100</v>
       </c>
     </row>
@@ -719,7 +723,7 @@
       <c r="B30" t="str">
         <v>Expected (per guest)</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="1">
         <v>150</v>
       </c>
     </row>
@@ -727,7 +731,7 @@
       <c r="B31" t="str">
         <v>Optimistic (per guest)</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="1">
         <v>220</v>
       </c>
     </row>
@@ -767,7 +771,7 @@
       <c r="B6" t="str">
         <v>Estimated banquet cost (GST &amp; service charge in)</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="1">
         <f>ROUND(INPUTS!C8*ROUND(INPUTS!C6/INPUTS!C7,0)*(1+INPUTS!C9)*(1+INPUTS!C10),0)</f>
         <v>0</v>
       </c>
@@ -779,7 +783,7 @@
       <c r="B7" t="str">
         <v>Non-banquet cost</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="1">
         <f>INPUTS!C25</f>
         <v>0</v>
       </c>
@@ -788,7 +792,7 @@
       <c r="B8" t="str">
         <v>TOTAL ESTIMATED EXPENDITURE</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="1">
         <f>ROUND(ROUND(INPUTS!C8*ROUND(INPUTS!C6/INPUTS!C7,0)*(1+INPUTS!C9)*(1+INPUTS!C10),0)+INPUTS!C25,0)</f>
         <v>0</v>
       </c>
@@ -816,15 +820,15 @@
       <c r="B12" t="str">
         <v>Conservative</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="1">
         <f>ROUND(INPUTS!C29,0)</f>
         <v>0</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="1">
         <f>ROUND(INPUTS!C6*INPUTS!C29,0)</f>
         <v>0</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="1">
         <f>ROUND(D12-$C8,0)</f>
         <v>0</v>
       </c>
@@ -833,15 +837,15 @@
       <c r="B13" t="str">
         <v>Expected</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="1">
         <f>ROUND(INPUTS!C30,0)</f>
         <v>0</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="1">
         <f>ROUND(INPUTS!C6*INPUTS!C30,0)</f>
         <v>0</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="1">
         <f>ROUND(D13-$C8,0)</f>
         <v>0</v>
       </c>
@@ -850,15 +854,15 @@
       <c r="B14" t="str">
         <v>Optimistic</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="1">
         <f>ROUND(INPUTS!C31,0)</f>
         <v>0</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="1">
         <f>ROUND(INPUTS!C6*INPUTS!C31,0)</f>
         <v>0</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="1">
         <f>ROUND(D14-$C8,0)</f>
         <v>0</v>
       </c>
@@ -872,7 +876,7 @@
       <c r="B17" t="str">
         <v>Break-even average ang bao per guest (to cover TOTAL expenditure)</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="1">
         <f>IF(INPUTS!C6=0,0,C8/INPUTS!C6)</f>
         <v>0</v>
       </c>
@@ -884,7 +888,7 @@
       <c r="B18" t="str">
         <v>Break-even ang bao to cover banquet ONLY</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="1">
         <f>IF(INPUTS!C6=0,0,C6/INPUTS!C6)</f>
         <v>0</v>
       </c>
@@ -913,7 +917,7 @@
       <c r="B22" t="str">
         <v>Upfront cash to secure BEFORE the day (total − expected ang bao)</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="1">
         <f>MAX(0,C8-D13)</f>
         <v>0</v>
       </c>
@@ -925,7 +929,7 @@
       <c r="B23" t="str">
         <v>Expected ang bao on the day</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="1">
         <f>D13</f>
         <v>0</v>
       </c>
@@ -950,7 +954,7 @@
       <c r="B27" t="str">
         <v>T-12 months · venue deposit</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="1">
         <v>8000</v>
       </c>
       <c r="D27" t="str">
@@ -961,7 +965,7 @@
       <c r="B28" t="str">
         <v>T-9 · bridal deposit</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="1">
         <v>1500</v>
       </c>
       <c r="D28" t="str">
@@ -972,7 +976,7 @@
       <c r="B29" t="str">
         <v>T-6 · décor deposit</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="1">
         <v>800</v>
       </c>
       <c r="D29" t="str">
@@ -983,7 +987,7 @@
       <c r="B30" t="str">
         <v>T-3 · venue balance</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="1">
         <v>15000</v>
       </c>
       <c r="D30" t="str">
@@ -994,7 +998,7 @@
       <c r="B31" t="str">
         <v>T-1 · photography/videography</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="1">
         <v>4000</v>
       </c>
       <c r="D31" t="str">
@@ -1005,7 +1009,7 @@
       <c r="B32" t="str">
         <v>T-0 · final vendors</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="1">
         <v>5000</v>
       </c>
       <c r="D32" t="str">
@@ -1016,7 +1020,7 @@
       <c r="B33" t="str">
         <v>Total pre-wedding payments scheduled</v>
       </c>
-      <c r="C33">
+      <c r="C33" s="1">
         <f>SUM(C27:C32)</f>
         <v>0</v>
       </c>
@@ -1057,7 +1061,7 @@
       <c r="B6" t="str">
         <v>Total estimated wedding expenditure</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="1">
         <f>CALCULATOR!C8</f>
         <v>0</v>
       </c>
@@ -1066,7 +1070,7 @@
       <c r="B7" t="str">
         <v>Total banquet cost</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="1">
         <f>CALCULATOR!C6</f>
         <v>0</v>
       </c>
@@ -1075,7 +1079,7 @@
       <c r="B8" t="str">
         <v>Total non-banquet cost</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="1">
         <f>CALCULATOR!C7</f>
         <v>0</v>
       </c>
@@ -1084,7 +1088,7 @@
       <c r="B9" t="str">
         <v>Expected ang bao (estimate)</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="1">
         <f>CALCULATOR!D13</f>
         <v>0</v>
       </c>
@@ -1093,7 +1097,7 @@
       <c r="B10" t="str">
         <v>Break-even average ang bao (per guest)</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="1">
         <f>CALCULATOR!C17</f>
         <v>0</v>
       </c>
@@ -1102,7 +1106,7 @@
       <c r="B11" t="str">
         <v>Upfront cash to secure before the day</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="1">
         <f>CALCULATOR!C22</f>
         <v>0</v>
       </c>
@@ -1127,11 +1131,11 @@
       <c r="B15" t="str">
         <v>Conservative</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="1">
         <f>CALCULATOR!D12</f>
         <v>0</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="1">
         <f>CALCULATOR!E12</f>
         <v>0</v>
       </c>
@@ -1140,11 +1144,11 @@
       <c r="B16" t="str">
         <v>Expected</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="1">
         <f>CALCULATOR!D13</f>
         <v>0</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="1">
         <f>CALCULATOR!E13</f>
         <v>0</v>
       </c>
@@ -1153,11 +1157,11 @@
       <c r="B17" t="str">
         <v>Optimistic</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="1">
         <f>CALCULATOR!D14</f>
         <v>0</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="1">
         <f>CALCULATOR!E14</f>
         <v>0</v>
       </c>
